--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T07:58:11+00:00</t>
+    <t>2026-04-08T15:08:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T15:08:35+00:00</t>
+    <t>2026-04-10T10:13:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T10:13:44+00:00</t>
+    <t>2026-04-10T13:55:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T13:55:47+00:00</t>
+    <t>2026-04-13T09:21:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:21:18+00:00</t>
+    <t>2026-04-15T12:54:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T12:54:49+00:00</t>
+    <t>2026-04-16T12:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T12:59:59+00:00</t>
+    <t>2026-04-16T13:39:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T13:39:21+00:00</t>
+    <t>2026-04-16T14:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T14:53:17+00:00</t>
+    <t>2026-04-16T16:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T16:01:15+00:00</t>
+    <t>2026-04-17T10:10:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T10:10:28+00:00</t>
+    <t>2026-04-29T06:12:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T06:12:43+00:00</t>
+    <t>2026-04-29T15:47:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T15:47:22+00:00</t>
+    <t>2026-04-29T18:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T18:06:39+00:00</t>
+    <t>2026-04-30T12:54:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
+++ b/ig/DM-AVRIL-2026/ASS-X14-AgregatDisciplineEquipementSocial.xlsx
@@ -56,7 +56,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T12:54:15+00:00</t>
+    <t>2026-05-04T12:07:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
